--- a/data/reports/all_rated_companies.xlsx
+++ b/data/reports/all_rated_companies.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -445,9 +445,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -730,27 +730,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>武汉奇安信科技有限公司</t>
+          <t>烽火通信科技股份有限公司</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>91420100MA4KXNYJ1C</t>
+          <t>914201007146661114</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5000万元</t>
+          <t>128921万元</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>网络安全技术开发、信息安全服务、软件开发、人工智能应用开发、云计算技术服务</t>
+          <t>光纤通信和相关通信技术、信息技术领域的科技开发；相关高新技术产品设计、制造和销售；系统集成</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>网络安全, 人工智能, 云计算</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -760,89 +760,89 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>智能制造, 数据中台, 供应链数字化</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>助力通信设备龙头打通研发-制造数据，加速数字化转型</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>技术投入、资金实力、转型意愿、团队规模等数据缺失，按该维度满分的一半计分；行业属于通信技术领域，数字化转型需求强烈，行业匹配度较高。综合得分为54分，处于C等级，建议暂缓或低成本维护。</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 14:47:19.895983</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>武汉极智嘉机器人有限公司</t>
+          <t>武汉创新云计算有限公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91420100MA4KXKQE5R</t>
+          <t>91420100MA4K5A4D6E</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2000万元</t>
+          <t>8000万元</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>智能机器人研发、人工智能技术开发、自动化系统集成、物联网技术服务、云计算</t>
+          <t>云计算平台、AI中台、系统集成</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>人工智能, 机器人, 物联网</t>
+          <t>云计算, AI中台, 系统集成</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -852,37 +852,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -907,34 +907,34 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 15:30:23.645408</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>远光软件(武汉)有限公司</t>
+          <t>武汉奇安信科技有限公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>91420100333557392D</t>
+          <t>91420100MA4KXNYJ1C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>500万元</t>
+          <t>5000万元</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>软件开发、信息技术咨询服务、计算机系统集成、大数据分析</t>
+          <t>网络安全技术开发、信息安全服务、软件开发、人工智能应用开发、云计算技术服务</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>网络安全, 人工智能, 云计算</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -944,22 +944,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1006,12 +1006,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>武汉融芯智能科技有限公司</t>
+          <t>武汉极智嘉机器人有限公司</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91420100MABTNX8857</t>
+          <t>91420100MA4KXKQE5R</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人工智能硬件开发、智能控制系统集成、人工智能通用应用系统开发、大数据服务</t>
+          <t>智能机器人研发、人工智能技术开发、自动化系统集成、物联网技术服务、云计算</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>人工智能, 机器人, 物联网</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1051,27 +1051,27 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1098,27 +1098,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>烽火通信科技股份有限公司</t>
+          <t>武汉智云科技有限公司</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>914201007146661114</t>
+          <t>91420100MA4K2X1A3B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>128921万元</t>
+          <t>5000万元</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>光纤通信和相关通信技术、信息技术领域的科技开发；相关高新技术产品设计、制造和销售；系统集成</t>
+          <t>人工智能软件开发、云计算、大数据分析</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>人工智能, 云计算</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1143,27 +1143,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1183,34 +1183,34 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 15:30:23.645408</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>武汉达梦数据库有限公司</t>
+          <t>武汉长飞光纤光缆股份有限公司</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>91420100737519378E</t>
+          <t>91420100616400222M</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7050万元</t>
+          <t>75000万元</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>数据库管理系统软件、数据集成软件、数据治理软件的研发、销售及技术服务；信息系统集成</t>
+          <t>光纤光缆研发制造、通信技术、信息技术开发、智能网络解决方案、数字化转型服务</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>通信技术, 信息技术, 数字化转型</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1282,27 +1282,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>武汉旷视金智科技有限公司</t>
+          <t>武汉星辰智能有限公司</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>91420100MA4KXMM02E</t>
+          <t>91420100MA4K7C6F8G</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1000万元</t>
+          <t>2000万元</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>人工智能技术开发、技术咨询、技术服务；计算机系统集成；软件开发</t>
+          <t>智能安防、物联网、软件开发</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>智能安防, 物联网, 软件开发</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1312,42 +1312,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1367,34 +1367,34 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 15:30:23.645408</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>武汉长飞光纤光缆股份有限公司</t>
+          <t>光谷数据科技有限公司</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>91420100616400222M</t>
+          <t>91420100MA4K3Y2B4C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>75000万元</t>
+          <t>1000万元</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>光纤光缆研发制造、通信技术、信息技术开发、智能网络解决方案、数字化转型服务</t>
+          <t>大数据平台开发、数字化转型咨询</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>通信技术, 信息技术, 数字化转型</t>
+          <t>大数据, 数字化转型</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1404,32 +1404,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,29 +1459,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 15:30:23.645408</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>武汉斗鱼网络科技有限公司</t>
+          <t>武汉百域人工智能科技有限公司</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>91420100333437374F</t>
+          <t>91420111MA4L0QBP9Q</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2234万元</t>
+          <t>3500万元</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>网络直播平台运营、互联网技术开发、软件开发、信息技术咨询服务、计算机系统集成</t>
+          <t>数字技术服务、信息系统集成服务、互联网数据服务、人工智能应用软件开发、人工智能公共服务平台技术咨询</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1511,27 +1511,27 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1551,29 +1551,29 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 14:41:49.624568</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>武汉百域人工智能科技有限公司</t>
+          <t>武汉融芯智能科技有限公司</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>91420111MA4L0QBP9Q</t>
+          <t>91420100MABTNX8857</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3500万元</t>
+          <t>2000万元</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>数字技术服务、信息系统集成服务、互联网数据服务、人工智能应用软件开发、人工智能公共服务平台技术咨询</t>
+          <t>人工智能硬件开发、智能控制系统集成、人工智能通用应用系统开发、大数据服务</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1603,29 +1603,29 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>—</t>
@@ -1643,19 +1643,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 14:41:49.624568</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>腾讯科技(武汉)有限公司</t>
+          <t>武汉旷视金智科技有限公司</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>91420100584872426J</t>
+          <t>91420100MA4KXMM02E</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>计算机软硬件技术开发、销售；互联网技术开发；信息技术咨询服务；网络游戏开发</t>
+          <t>人工智能技术开发、技术咨询、技术服务；计算机系统集成；软件开发</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 14:41:49.624568</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>武汉爱迪软件技术有限公司</t>
+          <t>武汉达梦数据库有限公司</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>91420100MA4F3N3H5N</t>
+          <t>91420100737519378E</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>500万元</t>
+          <t>7050万元</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>智慧检务软件产品开发、信息系统集成服务、软件开发、信息技术咨询</t>
+          <t>数据库管理系统软件、数据集成软件、数据治理软件的研发、销售及技术服务；信息系统集成</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 14:41:49.624568</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1879,47 +1879,783 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:41:49.624568</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>远光软件(武汉)有限公司</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>91420100333557392D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>500万元</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>软件开发、信息技术咨询服务、计算机系统集成、大数据分析</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:41:49.624568</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>武汉斗鱼网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>91420100333437374F</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2234万元</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>网络直播平台运营、互联网技术开发、软件开发、信息技术咨询服务、计算机系统集成</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:41:49.624568</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>武汉爱迪软件技术有限公司</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91420100MA4F3N3H5N</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>500万元</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>智慧检务软件产品开发、信息系统集成服务、软件开发、信息技术咨询</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:41:49.624568</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>武汉大数据产业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>大数据</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2026-08-06 15:30:23.645408</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>武汉云端科技有限公司</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91420100MA4L0F9I1J</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3000万元</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>云原生开发、DevOps、容器化</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>云原生, DevOps</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-08-06 15:30:23.645408</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>腾讯科技(武汉)有限公司</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91420100584872426J</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1000万元</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>计算机软硬件技术开发、销售；互联网技术开发；信息技术咨询服务；网络游戏开发</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-08-04 12:35:18.778131</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:41:49.624568</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>武汉华信软件有限公司</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>91420100MA4K4Z3C5D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>300万元</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>网络工程、硬件销售、监控设备</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>网络工程, 硬件</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2026-08-06 15:30:23.645408</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>武汉老牌软件有限公司</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>91420100MA4L1G0J2K</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>800万元</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>传统ERP开发、软件外包</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>软件开发, 外包</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2026-08-06 15:30:23.645408</t>
         </is>
       </c>
     </row>

--- a/data/reports/all_rated_companies.xlsx
+++ b/data/reports/all_rated_companies.xlsx
@@ -445,9 +445,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -546,27 +546,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>武汉光谷信息技术股份有限公司</t>
+          <t>武汉长飞光纤光缆股份有限公司</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91420100663491955X</t>
+          <t>91420100616400222M</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5100万元</t>
+          <t>75000万元</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>地理信息系统、遥感技术服务、软件开发、信息技术咨询服务、计算机系统集成、大数据分析</t>
+          <t>光纤光缆研发制造、通信技术、信息技术开发、智能网络解决方案、数字化转型服务</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>信息技术, 软件开发, 大数据</t>
+          <t>通信技术, 信息技术, 数字化转型</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -581,34 +581,34 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>6</t>
@@ -631,34 +631,34 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>武汉木仓科技股份有限公司</t>
+          <t>武汉奇安信科技有限公司</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91420100333569880Q</t>
+          <t>91420100MA4KXNYJ1C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3000万元</t>
+          <t>5000万元</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>互联网信息服务、软件开发、人工智能应用开发、大数据分析、智能驾驶辅助系统</t>
+          <t>网络安全技术开发、信息安全服务、软件开发、人工智能应用开发、云计算技术服务</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>互联网, 人工智能, 大数据</t>
+          <t>网络安全, 人工智能, 云计算</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -668,32 +668,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,29 +723,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>烽火通信科技股份有限公司</t>
+          <t>武汉融芯智能科技有限公司</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>914201007146661114</t>
+          <t>91420100MABTNX8857</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>128921万元</t>
+          <t>2000万元</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>光纤通信和相关通信技术、信息技术领域的科技开发；相关高新技术产品设计、制造和销售；系统集成</t>
+          <t>人工智能硬件开发、智能控制系统集成、人工智能通用应用系统开发、大数据服务</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -760,89 +760,89 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>智能制造, 数据中台, 供应链数字化</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>助力通信设备龙头打通研发-制造数据，加速数字化转型</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>技术投入、资金实力、转型意愿、团队规模等数据缺失，按该维度满分的一半计分；行业属于通信技术领域，数字化转型需求强烈，行业匹配度较高。综合得分为54分，处于C等级，建议暂缓或低成本维护。</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-06 14:47:19.895983</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>武汉创新云计算有限公司</t>
+          <t>武汉木仓科技股份有限公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91420100MA4K5A4D6E</t>
+          <t>91420100333569880Q</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8000万元</t>
+          <t>3000万元</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>云计算平台、AI中台、系统集成</t>
+          <t>互联网信息服务、软件开发、人工智能应用开发、大数据分析、智能驾驶辅助系统</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>云计算, AI中台, 系统集成</t>
+          <t>互联网, 人工智能, 大数据</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -907,34 +907,34 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-06 15:30:23.645408</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>武汉奇安信科技有限公司</t>
+          <t>武汉极智嘉机器人有限公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>91420100MA4KXNYJ1C</t>
+          <t>91420100MA4KXKQE5R</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5000万元</t>
+          <t>2000万元</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>网络安全技术开发、信息安全服务、软件开发、人工智能应用开发、云计算技术服务</t>
+          <t>智能机器人研发、人工智能技术开发、自动化系统集成、物联网技术服务、云计算</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>网络安全, 人工智能, 云计算</t>
+          <t>人工智能, 机器人, 物联网</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -959,29 +959,29 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>—</t>
@@ -999,34 +999,34 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>武汉极智嘉机器人有限公司</t>
+          <t>武汉光谷信息技术股份有限公司</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91420100MA4KXKQE5R</t>
+          <t>91420100663491955X</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2000万元</t>
+          <t>5100万元</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>智能机器人研发、人工智能技术开发、自动化系统集成、物联网技术服务、云计算</t>
+          <t>地理信息系统、遥感技术服务、软件开发、信息技术咨询服务、计算机系统集成、大数据分析</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人工智能, 机器人, 物联网</t>
+          <t>信息技术, 软件开发, 大数据</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1091,34 +1091,34 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>武汉智云科技有限公司</t>
+          <t>武汉创新云计算有限公司</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>91420100MA4K2X1A3B</t>
+          <t>91420100MA4K5A4D6E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5000万元</t>
+          <t>8000万元</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人工智能软件开发、云计算、大数据分析</t>
+          <t>云计算平台、AI中台、系统集成</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>人工智能, 云计算</t>
+          <t>云计算, AI中台, 系统集成</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1190,27 +1190,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>武汉长飞光纤光缆股份有限公司</t>
+          <t>烽火通信科技股份有限公司</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>91420100616400222M</t>
+          <t>914201007146661114</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>75000万元</t>
+          <t>128921万元</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>光纤光缆研发制造、通信技术、信息技术开发、智能网络解决方案、数字化转型服务</t>
+          <t>光纤通信和相关通信技术、信息技术领域的科技开发；相关高新技术产品设计、制造和销售；系统集成</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>通信技术, 信息技术, 数字化转型</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1220,42 +1220,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,34 +1275,34 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-04 12:35:18.778131</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>武汉星辰智能有限公司</t>
+          <t>武汉智云科技有限公司</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>91420100MA4K7C6F8G</t>
+          <t>91420100MA4K2X1A3B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2000万元</t>
+          <t>5000万元</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>智能安防、物联网、软件开发</t>
+          <t>人工智能软件开发、云计算、大数据分析</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>智能安防, 物联网, 软件开发</t>
+          <t>人工智能, 云计算</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1317,37 +1317,37 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1374,27 +1374,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>光谷数据科技有限公司</t>
+          <t>远光软件(武汉)有限公司</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>91420100MA4K3Y2B4C</t>
+          <t>91420100333557392D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1000万元</t>
+          <t>500万元</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>大数据平台开发、数字化转型咨询</t>
+          <t>软件开发、信息技术咨询服务、计算机系统集成、大数据分析</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>大数据, 数字化转型</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1424,22 +1424,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,29 +1459,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-06 15:30:23.645408</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>武汉百域人工智能科技有限公司</t>
+          <t>武汉爱迪软件技术有限公司</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>91420111MA4L0QBP9Q</t>
+          <t>91420100MA4F3N3H5N</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3500万元</t>
+          <t>500万元</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>数字技术服务、信息系统集成服务、互联网数据服务、人工智能应用软件开发、人工智能公共服务平台技术咨询</t>
+          <t>智慧检务软件产品开发、信息系统集成服务、软件开发、信息技术咨询</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1496,42 +1496,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1551,29 +1551,29 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>武汉融芯智能科技有限公司</t>
+          <t>武汉百域人工智能科技有限公司</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>91420100MABTNX8857</t>
+          <t>91420111MA4L0QBP9Q</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2000万元</t>
+          <t>3500万元</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>人工智能硬件开发、智能控制系统集成、人工智能通用应用系统开发、大数据服务</t>
+          <t>数字技术服务、信息系统集成服务、互联网数据服务、人工智能应用软件开发、人工智能公共服务平台技术咨询</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1588,17 +1588,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1608,22 +1608,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1643,34 +1643,34 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>武汉旷视金智科技有限公司</t>
+          <t>武汉星辰智能有限公司</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>91420100MA4KXMM02E</t>
+          <t>91420100MA4K7C6F8G</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1000万元</t>
+          <t>2000万元</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>人工智能技术开发、技术咨询、技术服务；计算机系统集成；软件开发</t>
+          <t>智能安防、物联网、软件开发</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>智能安防, 物联网, 软件开发</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 15:30:23.645408</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>武汉达梦数据库有限公司</t>
+          <t>武汉旷视金智科技有限公司</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>91420100737519378E</t>
+          <t>91420100MA4KXMM02E</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7050万元</t>
+          <t>1000万元</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>数据库管理系统软件、数据集成软件、数据治理软件的研发、销售及技术服务；信息系统集成</t>
+          <t>人工智能技术开发、技术咨询、技术服务；计算机系统集成；软件开发</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1787,19 +1787,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>5</t>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1827,34 +1827,34 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>武汉灿宇未来科技有限公司</t>
+          <t>光谷数据科技有限公司</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>91420111MA49RM6Q01</t>
+          <t>91420100MA4K3Y2B4C</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100万元</t>
+          <t>1000万元</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>信息技术咨询服务、软件开发、人工智能基础软件开发、网络技术服务</t>
+          <t>大数据平台开发、数字化转型咨询</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>大数据, 数字化转型</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1869,34 +1869,34 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>4</t>
@@ -1919,29 +1919,29 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 15:30:23.645408</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>远光软件(武汉)有限公司</t>
+          <t>武汉达梦数据库有限公司</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>91420100333557392D</t>
+          <t>91420100737519378E</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>500万元</t>
+          <t>7050万元</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>软件开发、信息技术咨询服务、计算机系统集成、大数据分析</t>
+          <t>数据库管理系统软件、数据集成软件、数据治理软件的研发、销售及技术服务；信息系统集成</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2011,29 +2011,29 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>武汉斗鱼网络科技有限公司</t>
+          <t>武汉灿宇未来科技有限公司</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>91420100333437374F</t>
+          <t>91420111MA49RM6Q01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2234万元</t>
+          <t>100万元</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>网络直播平台运营、互联网技术开发、软件开发、信息技术咨询服务、计算机系统集成</t>
+          <t>信息技术咨询服务、软件开发、人工智能基础软件开发、网络技术服务</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2048,37 +2048,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2103,29 +2103,29 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>武汉爱迪软件技术有限公司</t>
+          <t>武汉斗鱼网络科技有限公司</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91420100MA4F3N3H5N</t>
+          <t>91420100333437374F</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>500万元</t>
+          <t>2234万元</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>智慧检务软件产品开发、信息系统集成服务、软件开发、信息技术咨询</t>
+          <t>网络直播平台运营、互联网技术开发、软件开发、信息技术咨询服务、计算机系统集成</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2140,17 +2140,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2160,19 +2160,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>4</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
@@ -2416,29 +2416,29 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>0</t>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-06 14:41:49.624568</t>
+          <t>2026-08-06 16:37:46.301656</t>
         </is>
       </c>
     </row>
